--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>91295</v>
+        <v>80121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R8" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>91295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R9" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647052</v>
+        <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755489</v>
+        <v>755286</v>
       </c>
       <c r="R12" t="n">
-        <v>7211713</v>
+        <v>7211500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647039</v>
+        <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755427</v>
+        <v>755489</v>
       </c>
       <c r="R13" t="n">
-        <v>7211755</v>
+        <v>7211713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647020</v>
+        <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755286</v>
+        <v>755427</v>
       </c>
       <c r="R14" t="n">
-        <v>7211500</v>
+        <v>7211755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647020</v>
+        <v>127647052</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755286</v>
+        <v>755489</v>
       </c>
       <c r="R12" t="n">
-        <v>7211500</v>
+        <v>7211713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647052</v>
+        <v>127647039</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755489</v>
+        <v>755427</v>
       </c>
       <c r="R13" t="n">
-        <v>7211713</v>
+        <v>7211755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647039</v>
+        <v>127647020</v>
       </c>
       <c r="B14" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755427</v>
+        <v>755286</v>
       </c>
       <c r="R14" t="n">
-        <v>7211755</v>
+        <v>7211500</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127647045</v>
       </c>
       <c r="B6" t="n">
-        <v>57765</v>
+        <v>57767</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B8" t="n">
-        <v>80121</v>
+        <v>91297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R8" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B9" t="n">
-        <v>91295</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R9" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>127647052</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>127647039</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>127647020</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>80123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R8" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>91297</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R9" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647052</v>
+        <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755489</v>
+        <v>755286</v>
       </c>
       <c r="R12" t="n">
-        <v>7211713</v>
+        <v>7211500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647039</v>
+        <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755427</v>
+        <v>755489</v>
       </c>
       <c r="R13" t="n">
-        <v>7211755</v>
+        <v>7211713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647020</v>
+        <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755286</v>
+        <v>755427</v>
       </c>
       <c r="R14" t="n">
-        <v>7211500</v>
+        <v>7211755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647020</v>
+        <v>127647052</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755286</v>
+        <v>755489</v>
       </c>
       <c r="R12" t="n">
-        <v>7211500</v>
+        <v>7211713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647052</v>
+        <v>127647039</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755489</v>
+        <v>755427</v>
       </c>
       <c r="R13" t="n">
-        <v>7211713</v>
+        <v>7211755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647039</v>
+        <v>127647020</v>
       </c>
       <c r="B14" t="n">
-        <v>80123</v>
+        <v>91338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755427</v>
+        <v>755286</v>
       </c>
       <c r="R14" t="n">
-        <v>7211755</v>
+        <v>7211500</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2143,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127647045</v>
       </c>
       <c r="B6" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>91306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R8" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B9" t="n">
-        <v>91303</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R9" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647052</v>
+        <v>127647039</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755489</v>
+        <v>755427</v>
       </c>
       <c r="R12" t="n">
-        <v>7211713</v>
+        <v>7211755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647039</v>
+        <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755427</v>
+        <v>755489</v>
       </c>
       <c r="R13" t="n">
-        <v>7211755</v>
+        <v>7211713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
         <v>127647020</v>
       </c>
       <c r="B14" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127647051</v>
+        <v>127647041</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755433</v>
+        <v>755510</v>
       </c>
       <c r="R15" t="n">
-        <v>7211746</v>
+        <v>7211778</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127647041</v>
+        <v>127647051</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755510</v>
+        <v>755433</v>
       </c>
       <c r="R16" t="n">
-        <v>7211778</v>
+        <v>7211746</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,7 +2143,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127647045</v>
       </c>
       <c r="B6" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127647017</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127647038</v>
       </c>
       <c r="B9" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647039</v>
+        <v>127647052</v>
       </c>
       <c r="B12" t="n">
-        <v>80126</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755427</v>
+        <v>755489</v>
       </c>
       <c r="R12" t="n">
-        <v>7211755</v>
+        <v>7211713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647052</v>
+        <v>127647039</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755489</v>
+        <v>755427</v>
       </c>
       <c r="R13" t="n">
-        <v>7211713</v>
+        <v>7211755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
         <v>127647020</v>
       </c>
       <c r="B14" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127647041</v>
+        <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>80126</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755510</v>
+        <v>755433</v>
       </c>
       <c r="R15" t="n">
-        <v>7211778</v>
+        <v>7211746</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127647051</v>
+        <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755433</v>
+        <v>755510</v>
       </c>
       <c r="R16" t="n">
-        <v>7211746</v>
+        <v>7211778</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,7 +2143,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>91314</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R8" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>91315</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R9" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647039</v>
+        <v>127647020</v>
       </c>
       <c r="B13" t="n">
-        <v>80132</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755427</v>
+        <v>755286</v>
       </c>
       <c r="R13" t="n">
-        <v>7211755</v>
+        <v>7211500</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647020</v>
+        <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>91349</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755286</v>
+        <v>755427</v>
       </c>
       <c r="R14" t="n">
-        <v>7211500</v>
+        <v>7211755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127647051</v>
+        <v>127647041</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755433</v>
+        <v>755510</v>
       </c>
       <c r="R15" t="n">
-        <v>7211746</v>
+        <v>7211778</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127647041</v>
+        <v>127647051</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755510</v>
+        <v>755433</v>
       </c>
       <c r="R16" t="n">
-        <v>7211778</v>
+        <v>7211746</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,7 +2143,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>91315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R8" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B9" t="n">
-        <v>91315</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R9" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647052</v>
+        <v>127647039</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755489</v>
+        <v>755427</v>
       </c>
       <c r="R12" t="n">
-        <v>7211713</v>
+        <v>7211755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647039</v>
+        <v>127647052</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755427</v>
+        <v>755489</v>
       </c>
       <c r="R14" t="n">
-        <v>7211755</v>
+        <v>7211713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>91315</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R8" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>91316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R9" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647039</v>
+        <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>91351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755427</v>
+        <v>755286</v>
       </c>
       <c r="R12" t="n">
-        <v>7211755</v>
+        <v>7211500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647020</v>
+        <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755286</v>
+        <v>755489</v>
       </c>
       <c r="R13" t="n">
-        <v>7211500</v>
+        <v>7211713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647052</v>
+        <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755489</v>
+        <v>755427</v>
       </c>
       <c r="R14" t="n">
-        <v>7211713</v>
+        <v>7211755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127647041</v>
+        <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755510</v>
+        <v>755433</v>
       </c>
       <c r="R15" t="n">
-        <v>7211778</v>
+        <v>7211746</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127647051</v>
+        <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755433</v>
+        <v>755510</v>
       </c>
       <c r="R16" t="n">
-        <v>7211746</v>
+        <v>7211778</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,7 +2143,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>91317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R8" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B9" t="n">
-        <v>91316</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R9" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647017</v>
+        <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>91317</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755288</v>
+        <v>755420</v>
       </c>
       <c r="R8" t="n">
-        <v>7211507</v>
+        <v>7211724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647038</v>
+        <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>91317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755420</v>
+        <v>755288</v>
       </c>
       <c r="R9" t="n">
-        <v>7211724</v>
+        <v>7211507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647020</v>
+        <v>127647039</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755286</v>
+        <v>755427</v>
       </c>
       <c r="R12" t="n">
-        <v>7211500</v>
+        <v>7211755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647052</v>
+        <v>127647020</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755489</v>
+        <v>755286</v>
       </c>
       <c r="R13" t="n">
-        <v>7211713</v>
+        <v>7211500</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647039</v>
+        <v>127647052</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755427</v>
+        <v>755489</v>
       </c>
       <c r="R14" t="n">
-        <v>7211755</v>
+        <v>7211713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647039</v>
+        <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755427</v>
+        <v>755286</v>
       </c>
       <c r="R12" t="n">
-        <v>7211755</v>
+        <v>7211500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647020</v>
+        <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755286</v>
+        <v>755489</v>
       </c>
       <c r="R13" t="n">
-        <v>7211500</v>
+        <v>7211713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647052</v>
+        <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755489</v>
+        <v>755427</v>
       </c>
       <c r="R14" t="n">
-        <v>7211713</v>
+        <v>7211755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647020</v>
+        <v>127647039</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755286</v>
+        <v>755427</v>
       </c>
       <c r="R12" t="n">
-        <v>7211500</v>
+        <v>7211755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647052</v>
+        <v>127647020</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755489</v>
+        <v>755286</v>
       </c>
       <c r="R13" t="n">
-        <v>7211713</v>
+        <v>7211500</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647039</v>
+        <v>127647052</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755427</v>
+        <v>755489</v>
       </c>
       <c r="R14" t="n">
-        <v>7211755</v>
+        <v>7211713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80161</v>
+        <v>80254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127647045</v>
       </c>
       <c r="B6" t="n">
-        <v>57776</v>
+        <v>57820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,14 +1177,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,14 +1278,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,14 +1379,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91317</v>
+        <v>91469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,14 +1480,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,14 +1586,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79061</v>
+        <v>79152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,14 +1687,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1748,14 +1788,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,14 +1889,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1942,14 +1990,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,14 +2091,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2136,14 +2192,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91710</v>
+        <v>91862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2233,7 +2293,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127647045</v>
       </c>
       <c r="B6" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127647045</v>
       </c>
       <c r="B6" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127647045</v>
       </c>
       <c r="B6" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127647045</v>
       </c>
       <c r="B6" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127647053</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127647029</v>
       </c>
       <c r="B4" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127647040</v>
       </c>
       <c r="B5" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127647054</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127647038</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127647042</v>
       </c>
       <c r="B10" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127647015</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>127647052</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127647039</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>127647051</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127647041</v>
       </c>
       <c r="B16" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127647019</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127647017</v>
       </c>
       <c r="B9" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127647020</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127647018</v>
       </c>
       <c r="B17" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127647019</v>
+        <v>127647015</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755288</v>
+        <v>755524</v>
       </c>
       <c r="R2" t="n">
-        <v>7211507</v>
+        <v>7211787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127647053</v>
+        <v>127647019</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755500</v>
+        <v>755288</v>
       </c>
       <c r="R3" t="n">
-        <v>7211753</v>
+        <v>7211507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127647029</v>
+        <v>127647020</v>
       </c>
       <c r="B4" t="n">
-        <v>80178</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755542</v>
+        <v>755286</v>
       </c>
       <c r="R4" t="n">
-        <v>7211786</v>
+        <v>7211500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127647040</v>
+        <v>127647018</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>92281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755443</v>
+        <v>755285</v>
       </c>
       <c r="R5" t="n">
-        <v>7211769</v>
+        <v>7211501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127647045</v>
+        <v>127647017</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755560</v>
+        <v>755288</v>
       </c>
       <c r="R6" t="n">
-        <v>7211781</v>
+        <v>7211507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,11 +1150,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2x</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,14 +1180,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127647054</v>
+        <v>127647051</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1220,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755505</v>
+        <v>755433</v>
       </c>
       <c r="R7" t="n">
-        <v>7211790</v>
+        <v>7211746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127647038</v>
+        <v>127647052</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1321,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755420</v>
+        <v>755489</v>
       </c>
       <c r="R8" t="n">
-        <v>7211724</v>
+        <v>7211713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127647017</v>
+        <v>127647053</v>
       </c>
       <c r="B9" t="n">
-        <v>91513</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755288</v>
+        <v>755500</v>
       </c>
       <c r="R9" t="n">
-        <v>7211507</v>
+        <v>7211753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127647042</v>
+        <v>127647054</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>755545</v>
+        <v>755505</v>
       </c>
       <c r="R10" t="n">
-        <v>7211787</v>
+        <v>7211790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,11 +1554,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127647015</v>
+        <v>127647038</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755524</v>
+        <v>755420</v>
       </c>
       <c r="R11" t="n">
-        <v>7211787</v>
+        <v>7211724</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127647020</v>
+        <v>127647039</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755286</v>
+        <v>755427</v>
       </c>
       <c r="R12" t="n">
-        <v>7211500</v>
+        <v>7211755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127647052</v>
+        <v>127647040</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755489</v>
+        <v>755443</v>
       </c>
       <c r="R13" t="n">
-        <v>7211713</v>
+        <v>7211769</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127647039</v>
+        <v>127647041</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755427</v>
+        <v>755510</v>
       </c>
       <c r="R14" t="n">
-        <v>7211755</v>
+        <v>7211778</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127647051</v>
+        <v>127647042</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755433</v>
+        <v>755545</v>
       </c>
       <c r="R15" t="n">
-        <v>7211746</v>
+        <v>7211787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,6 +2059,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127647041</v>
+        <v>127647043</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755510</v>
+        <v>755568</v>
       </c>
       <c r="R16" t="n">
-        <v>7211778</v>
+        <v>7211785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,32 +2195,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647018</v>
+        <v>127647029</v>
       </c>
       <c r="B17" t="n">
-        <v>91920</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755285</v>
+        <v>755542</v>
       </c>
       <c r="R17" t="n">
-        <v>7211501</v>
+        <v>7211786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,6 +2289,112 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127647045</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mullkälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>755560</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7211781</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 913-2023 artfynd.xlsx
+++ b/artfynd/A 913-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647015</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647020</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647018</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647017</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647051</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647052</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647053</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647054</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647038</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647039</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647040</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647041</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647042</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647043</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647029</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2399,8 +2484,32 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127647045</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>